--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T09:04:28+00:00</t>
+    <t>2024-10-26T11:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:58:28+00:00</t>
+    <t>2024-10-26T12:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:16:12+00:00</t>
+    <t>2024-10-26T12:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:32:55+00:00</t>
+    <t>2024-10-26T13:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:09:27+00:00</t>
+    <t>2024-10-26T13:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:28:10+00:00</t>
+    <t>2024-10-26T14:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="236">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T14:16:20+00:00</t>
+    <t>2024-10-26T14:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -340,6 +340,22 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Address.extension:municipalityCode</t>
+  </si>
+  <si>
+    <t>municipalityCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-address-municipalityCode}
+</t>
+  </si>
+  <si>
+    <t>Address Municipality Code</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -1039,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.23046875" customWidth="true" bestFit="true"/>
@@ -1550,9 +1566,11 @@
         <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="D5" t="s" s="2">
         <v>21</v>
       </c>
@@ -1567,10 +1585,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>108</v>
@@ -1581,12 +1599,8 @@
       <c r="M5" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
       </c>
@@ -1598,7 +1612,7 @@
         <v>21</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="U5" t="s" s="2">
         <v>21</v>
@@ -1610,13 +1624,13 @@
         <v>21</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>21</v>
@@ -1634,28 +1648,28 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>21</v>
@@ -1663,10 +1677,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1683,24 +1697,26 @@
         <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="O6" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="O6" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="P6" t="s" s="2">
         <v>21</v>
       </c>
@@ -1712,7 +1728,7 @@
         <v>21</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>21</v>
@@ -1724,13 +1740,13 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
@@ -1748,7 +1764,7 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1760,27 +1776,27 @@
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1800,23 +1816,21 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>21</v>
       </c>
@@ -1828,7 +1842,7 @@
         <v>21</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="U7" t="s" s="2">
         <v>21</v>
@@ -1840,13 +1854,13 @@
         <v>21</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>21</v>
@@ -1864,7 +1878,7 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1876,27 +1890,27 @@
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1907,7 +1921,7 @@
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -1916,19 +1930,23 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O8" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P8" t="s" s="2">
         <v>21</v>
       </c>
@@ -1940,75 +1958,75 @@
         <v>21</v>
       </c>
       <c r="T8" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="U8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK8" t="s" s="2">
+      <c r="AM8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2019,7 +2037,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2028,16 +2046,16 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2052,7 +2070,7 @@
         <v>21</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="U9" t="s" s="2">
         <v>21</v>
@@ -2088,39 +2106,39 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2131,7 +2149,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -2143,13 +2161,13 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2188,29 +2206,31 @@
         <v>21</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AC10" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -2227,14 +2247,12 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2243,7 +2261,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2255,13 +2273,13 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2300,16 +2318,14 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>104</v>
@@ -2330,7 +2346,7 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>21</v>
@@ -2344,10 +2360,10 @@
         <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -2369,13 +2385,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2444,7 +2460,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
@@ -2455,13 +2471,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>21</v>
@@ -2483,10 +2499,10 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>168</v>
@@ -2572,7 +2588,7 @@
         <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>171</v>
@@ -2603,7 +2619,7 @@
         <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2672,7 +2688,7 @@
         <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -2686,9 +2702,11 @@
         <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2709,13 +2727,13 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2739,7 +2757,7 @@
         <v>21</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
         <v>21</v>
@@ -2766,19 +2784,19 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>21</v>
@@ -2802,7 +2820,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2818,16 +2836,16 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2842,43 +2860,43 @@
         <v>21</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2890,38 +2908,38 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -2930,20 +2948,18 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -2956,7 +2972,7 @@
         <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>21</v>
@@ -2992,7 +3008,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3004,38 +3020,38 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3044,18 +3060,20 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3068,7 +3086,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -3104,7 +3122,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3116,31 +3134,31 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="AM18" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3156,16 +3174,16 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3180,7 +3198,7 @@
         <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3216,7 +3234,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3228,31 +3246,31 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3268,20 +3286,18 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3294,7 +3310,7 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -3330,7 +3346,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3342,27 +3358,27 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3373,7 +3389,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3382,21 +3398,21 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3408,7 +3424,7 @@
         <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>21</v>
@@ -3444,7 +3460,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3456,18 +3472,132 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="L22" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T14:33:31+00:00</t>
+    <t>2024-10-30T15:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T15:48:47+00:00</t>
+    <t>2024-11-17T20:47:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:47:41+00:00</t>
+    <t>2024-11-17T21:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:11:32+00:00</t>
+    <t>2024-11-17T21:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:35:06+00:00</t>
+    <t>2024-11-27T13:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:18:58+00:00</t>
+    <t>2024-12-15T14:03:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T14:03:14+00:00</t>
+    <t>2024-12-19T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T08:32:44+00:00</t>
+    <t>2025-01-08T14:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:32:12+00:00</t>
+    <t>2025-01-24T13:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T13:05:30+00:00</t>
+    <t>2025-01-24T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:13:16+00:00</t>
+    <t>2025-01-27T12:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T09:10:20+00:00</t>
+    <t>2026-03-01T19:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:31:53+00:00</t>
+    <t>2026-07-17T05:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
